--- a/asistencia_SCL.xlsx
+++ b/asistencia_SCL.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -58,9 +61,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -427,194 +431,5401 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A5:K8"/>
+  <dimension ref="A1:S64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="21" customWidth="1" min="19" max="19"/>
+  </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CIUDAD</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>SCL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Asistencias</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>SCL</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Vessel</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>ETA</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>First Name</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Last Name</t>
         </is>
       </c>
-      <c r="E5" s="1" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="F5" s="1" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Asistencia</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Transportes</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Comidas</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>Nro Vuelo Arribo</t>
         </is>
       </c>
-      <c r="G5" s="1" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>Fecha Vuelo Arribo</t>
         </is>
       </c>
-      <c r="H5" s="1" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>Hora Arribo</t>
         </is>
       </c>
-      <c r="I5" s="1" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Hotel</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Habitación</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>Date Pick Up</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>Hora Pick Up</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>Nro Vuelo Salida</t>
         </is>
       </c>
-      <c r="J5" s="1" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>Fecha Vuelo Salida</t>
         </is>
       </c>
-      <c r="K5" s="1" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>Hora Vuelo Salida</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Silver Endeavour</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KAPOMBE </t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> MIREILLE</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>LA8207</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 01:25:00</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr"/>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>LA91</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-14 04:32:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Silver Endeavour</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>DIAZ CASTILLO</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> MANUEL</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>TRIPULANTE</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>LA2377</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-14 05:40:00</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>LA87</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-15 11:22:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Silver Endeavour</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>HANSEN-LINDSTROM</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ULF-PETER MAGNUS</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>TRIPULANTE</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>LA8030</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-15 05:25:00</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr"/>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>LA83</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-16 09:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Silver Endeavour</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>SCHMIDT</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> FRANZISKA</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>TRIPULANTE</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>LA8104</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-14 15:00:00</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>LA89</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-17 19:46:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Silver Endeavour</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>AHMED</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ALTAF</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>TRIPULANTE</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>LA8207</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-14 01:25:00</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr"/>
+      <c r="P10" s="3" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>LA91</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-18 04:32:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Silver Endeavour</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>AJIMON</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ANANTHAKRISHNAN</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>TRIPULANTE</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>LA8207</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-14 01:25:00</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>LA91</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-19 04:32:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Silver Endeavour</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>BISHT</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> LALIT</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>TRIPULANTE</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>LA8207</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-14 01:25:00</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr"/>
+      <c r="P12" s="3" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>LA91</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-20 11:22:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Silver Endeavour</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>BOGA</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> FREADY HOMI</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>TRIPULANTE</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>LA763</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 18:34:00</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>LA95</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-21 09:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Silver Endeavour</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>FERNANDES</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ROYSTON</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>TRIPULANTE</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>LA763</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 18:34:00</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr"/>
+      <c r="P14" s="3" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>LA95</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-22 19:46:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Silver Endeavour</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KALIM </t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> MAZHAR</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>TRIPULANTE</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>LA8207</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-14 01:25:00</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>LA91</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-23 04:32:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Silver Endeavour</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>NORONHA</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> BONIFACIO JOAO</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>TRIPULANTE</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>LA8207</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-14 01:25:00</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr"/>
+      <c r="P16" s="3" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>LA91</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-24 04:32:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Silver Endeavour</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>SAHA</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> SOUVIK</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>TRIPULANTE</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>LA8207</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-14 01:25:00</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr"/>
+      <c r="P17" s="3" t="inlineStr"/>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>LA91</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-25 11:22:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Silver Endeavour</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>VELANKOVIL RAJU</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RENJITH MON</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>TRIPULANTE</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>LA8207</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-14 01:25:00</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr"/>
+      <c r="P18" s="3" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>LA91</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-26 09:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Silver Endeavour</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>ADNYANA</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PUTU WIDYA</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>TRIPULANTE</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>LA8207</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-14 01:25:00</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr"/>
+      <c r="P19" s="3" t="inlineStr"/>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>LA91</t>
+        </is>
+      </c>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-27 19:46:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Silver Endeavour</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>BOCCIA</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ANTONIO</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>TRIPULANTE</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>LA8207</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-14 01:25:00</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr"/>
+      <c r="P20" s="3" t="inlineStr"/>
+      <c r="Q20" s="3" t="inlineStr">
+        <is>
+          <t>LA91</t>
+        </is>
+      </c>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-28 04:32:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Silver Endeavour</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>GULINO</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> SIMONE</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>TRIPULANTE</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>LA8030</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-15 05:25:00</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr"/>
+      <c r="P21" s="3" t="inlineStr"/>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t>LA83</t>
+        </is>
+      </c>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-29 04:32:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Silver Endeavour</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>MASILI</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ANGELO</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>TRIPULANTE</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>LA8207</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 01:25:00</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr"/>
+      <c r="P22" s="3" t="inlineStr"/>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t>LA91</t>
+        </is>
+      </c>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-30 11:22:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Silver Endeavour</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>NYARIKI</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> MARTIN</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>TRIPULANTE</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>LA8207</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-14 01:25:00</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr"/>
+      <c r="P23" s="3" t="inlineStr"/>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t>LA91</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-01 09:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Silver Endeavour</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>OWIYO</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ERICK ODONGO</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>TRIPULANTE</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>LA763</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-14 18:34:00</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr"/>
+      <c r="P24" s="3" t="inlineStr"/>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t>LA95</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-02 19:46:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Silver Endeavour</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>AGUSTIN</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> GARRY</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>TRIPULANTE</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>AF406</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 09:50:00</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr"/>
+      <c r="P25" s="3" t="inlineStr"/>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t>LA295</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-03 04:32:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Silver Endeavour</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>AREVALO</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TIMOTEO JR. BARNES</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>AF406</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 09:50:00</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr"/>
+      <c r="P26" s="3" t="inlineStr"/>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t>LA295</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-03 04:32:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Silver Endeavour</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>BARLAAN</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> MARLON</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>AF406</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 09:50:00</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr"/>
+      <c r="P27" s="3" t="inlineStr"/>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t>LA295</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-05 11:22:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Silver Endeavour</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>CASTILLON</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> JOLLY PANTORILLA</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>AF406</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 09:50:00</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr"/>
+      <c r="P28" s="3" t="inlineStr"/>
+      <c r="Q28" s="3" t="inlineStr">
+        <is>
+          <t>LA295</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-05 11:22:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Silver Endeavour</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>GAY-YA</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> FELICIANA</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>AF406</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 09:50:00</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr"/>
+      <c r="P29" s="3" t="inlineStr"/>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t>LA295</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-05 11:22:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Silver Endeavour</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>GROMIO</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> KIMBERLY PANUGAO</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>AF406</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 09:50:00</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr"/>
+      <c r="P30" s="3" t="inlineStr"/>
+      <c r="Q30" s="3" t="inlineStr">
+        <is>
+          <t>LA295</t>
+        </is>
+      </c>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-05 11:22:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Silver Endeavour</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>HULLANA</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RAYMUND GARRIDO</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>AF406</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 09:50:00</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr"/>
+      <c r="P31" s="3" t="inlineStr"/>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
+          <t>LA295</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-05 11:22:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Silver Endeavour</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>LAURENTE</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> REYMARK</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>AF406</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 09:50:00</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr"/>
+      <c r="P32" s="3" t="inlineStr"/>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t>LA295</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-05 11:22:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Silver Endeavour</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>MACAPOBRE</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> HOMBRE</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>AF406</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 09:50:00</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr"/>
+      <c r="P33" s="3" t="inlineStr"/>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t>LA295</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-11 09:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Silver Endeavour</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>MAGDADARO</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RAFFY</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>AF406</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 09:50:00</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr"/>
+      <c r="P34" s="3" t="inlineStr"/>
+      <c r="Q34" s="3" t="inlineStr">
+        <is>
+          <t>LA295</t>
+        </is>
+      </c>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-11 09:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Silver Endeavour</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>NAVARRETE</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RUEL</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>AF406</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 09:50:00</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr"/>
+      <c r="P35" s="3" t="inlineStr"/>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t>LA295</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-11 09:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Silver Endeavour</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>NUNEZ</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> SHELLA GADUGDUG</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>AF406</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 09:50:00</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr"/>
+      <c r="P36" s="3" t="inlineStr"/>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
+          <t>LA295</t>
+        </is>
+      </c>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-11 09:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Silver Endeavour</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>ORFANO</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> NICANOR PANERGO</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>AF406</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 09:50:00</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr"/>
+      <c r="P37" s="3" t="inlineStr"/>
+      <c r="Q37" s="3" t="inlineStr">
+        <is>
+          <t>LA295</t>
+        </is>
+      </c>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-11 09:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Silver Endeavour</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>SAMSON</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PAUL ALDRIN </t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>AF406</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 09:50:00</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr"/>
+      <c r="P38" s="3" t="inlineStr"/>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t>LA295</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-16 09:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Silver Endeavour</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>VALENCIA</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ALFIE TRISTAN</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>AF406</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 09:50:00</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr"/>
+      <c r="P39" s="3" t="inlineStr"/>
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
+          <t>LA295</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-16 09:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Silver Endeavour</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>VILLA</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ORLANDO</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>AF406</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 09:50:00</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr"/>
+      <c r="P40" s="3" t="inlineStr"/>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t>LA295</t>
+        </is>
+      </c>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-16 09:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Silver Endeavour</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>BORDEI</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> SILVIU DUMITRU</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>AF406</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 09:50:00</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr"/>
+      <c r="P41" s="3" t="inlineStr"/>
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t>LA295</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-16 09:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Silver Endeavour</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>BENTHOTA DEVAGE</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> UDARA MADUSAKA</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>LA763</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-14 18:34:00</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr"/>
+      <c r="P42" s="3" t="inlineStr"/>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t>LA95</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-20 11:22:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>C-GEAI</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>CHARLES</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>CHAMPOUX</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>KL701</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-14 10:50:00</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr"/>
+      <c r="P43" s="3" t="inlineStr"/>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>C-GEAI</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>ZACHARY</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>COLLINS</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>LA8207</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-18 01:25:00</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr"/>
+      <c r="P44" s="3" t="inlineStr"/>
+      <c r="Q44" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>C-GEAI</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>MIREILLE</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>PAQUETTE</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>LA8030</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-18 05:25:00</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr"/>
+      <c r="P45" s="3" t="inlineStr"/>
+      <c r="Q45" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>C-GEAI</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>JEREMY</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>MARSOLAIS</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>QF3877</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-15 14:10:00</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr"/>
+      <c r="P46" s="3" t="inlineStr"/>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>C-FMKB</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>STEPHEN</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>KAIZER</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>AF406</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-18 09:50:00</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr"/>
+      <c r="P47" s="3" t="inlineStr"/>
+      <c r="Q47" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R47" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S47" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>C-FMKB</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>RYAN</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>WIENS</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>AF406</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-18 09:50:00</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr"/>
+      <c r="P48" s="3" t="inlineStr"/>
+      <c r="Q48" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R48" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S48" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>C-FMKB</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>STEPHEN</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>WHEATCROFT</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>AF406</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-18 09:50:00</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr"/>
+      <c r="P49" s="3" t="inlineStr"/>
+      <c r="Q49" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R49" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S49" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>C-FMKB</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>AYDEN</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>AF406</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-18 09:50:00</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr"/>
+      <c r="P50" s="3" t="inlineStr"/>
+      <c r="Q50" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R50" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S50" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Silver Cloud</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>MAURICE PHILIPPE</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>VAN DE MAELE BELLO</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>AF406</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-18 09:50:00</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr"/>
+      <c r="P51" s="3" t="inlineStr"/>
+      <c r="Q51" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R51" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S51" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Silver Cloud</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>CHEN</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> QI</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>LA533</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-14 07:00:00</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr"/>
+      <c r="P52" s="3" t="inlineStr"/>
+      <c r="Q52" s="3" t="inlineStr">
+        <is>
+          <t>LA87</t>
+        </is>
+      </c>
+      <c r="R52" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="S52" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-30 19:46:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Silver Cloud</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>NAULAK</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> GINKHUALLIAN</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>LA8030</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-18 04:15:00</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="inlineStr"/>
+      <c r="P53" s="3" t="inlineStr"/>
+      <c r="Q53" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S53" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Silver Cloud</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>ARKANI</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ADIN</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>LA8030</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-18 05:25:00</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="inlineStr"/>
+      <c r="P54" s="3" t="inlineStr"/>
+      <c r="Q54" s="3" t="inlineStr">
+        <is>
+          <t>LA81</t>
+        </is>
+      </c>
+      <c r="R54" s="3" t="inlineStr">
+        <is>
+          <t>2025-01-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="S54" s="3" t="inlineStr">
+        <is>
+          <t>2025-01-01 04:33:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Silver Cloud</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>PERMANA</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> HILMAN JAYA</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>LA8030</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-18 01:25:00</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr"/>
+      <c r="P55" s="3" t="inlineStr"/>
+      <c r="Q55" s="3" t="inlineStr">
+        <is>
+          <t>LA303</t>
+        </is>
+      </c>
+      <c r="R55" s="3" t="inlineStr">
+        <is>
+          <t>2025-01-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="S55" s="3" t="inlineStr">
+        <is>
+          <t>2025-01-02 19:53:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Silver Cloud</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>BARNABA</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> COSIMO</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>AF406</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 09:50:00</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O56" s="3" t="inlineStr"/>
+      <c r="P56" s="3" t="inlineStr"/>
+      <c r="Q56" s="3" t="inlineStr">
+        <is>
+          <t>LA83</t>
+        </is>
+      </c>
+      <c r="R56" s="3" t="inlineStr">
+        <is>
+          <t>2025-01-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="S56" s="3" t="inlineStr">
+        <is>
+          <t>2025-01-03 11:17:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Silver Cloud</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>GRANT</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> HARRY KEITH</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>KL701</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-18 10:50:00</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O57" s="3" t="inlineStr"/>
+      <c r="P57" s="3" t="inlineStr"/>
+      <c r="Q57" s="3" t="inlineStr">
+        <is>
+          <t>LA83</t>
+        </is>
+      </c>
+      <c r="R57" s="3" t="inlineStr">
+        <is>
+          <t>2025-01-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="S57" s="3" t="inlineStr">
+        <is>
+          <t>2025-01-04 19:46:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Silver Cloud</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>ALDAY</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> JEROME CARANDANG</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>KL701</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-18 10:50:00</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O58" s="3" t="inlineStr"/>
+      <c r="P58" s="3" t="inlineStr"/>
+      <c r="Q58" s="3" t="inlineStr">
+        <is>
+          <t>LA83</t>
+        </is>
+      </c>
+      <c r="R58" s="3" t="inlineStr">
+        <is>
+          <t>2025-01-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="S58" s="3" t="inlineStr">
+        <is>
+          <t>2025-01-05 16:31:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Silver Cloud</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>DELA CRUZ</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> LITO</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>KL701</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-18 11:25:00</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O59" s="3" t="inlineStr"/>
+      <c r="P59" s="3" t="inlineStr"/>
+      <c r="Q59" s="3" t="inlineStr">
+        <is>
+          <t>LA83</t>
+        </is>
+      </c>
+      <c r="R59" s="3" t="inlineStr">
+        <is>
+          <t>2025-01-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="S59" s="3" t="inlineStr">
+        <is>
+          <t>2025-01-06 16:31:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Silver Cloud</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>ISIDORO</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ROVAN</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>KL701</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-14 10:50:00</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O60" s="3" t="inlineStr"/>
+      <c r="P60" s="3" t="inlineStr"/>
+      <c r="Q60" s="3" t="inlineStr">
+        <is>
+          <t>LA83</t>
+        </is>
+      </c>
+      <c r="R60" s="3" t="inlineStr">
+        <is>
+          <t>2025-01-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="S60" s="3" t="inlineStr">
+        <is>
+          <t>2025-01-08 16:31:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Silver Cloud</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>NACARIO</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ESTER</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>LA705</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-14 09:20:00</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O61" s="3" t="inlineStr"/>
+      <c r="P61" s="3" t="inlineStr"/>
+      <c r="Q61" s="3" t="inlineStr">
+        <is>
+          <t>LA83</t>
+        </is>
+      </c>
+      <c r="R61" s="3" t="inlineStr">
+        <is>
+          <t>2025-01-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="S61" s="3" t="inlineStr">
+        <is>
+          <t>2025-01-08 16:31:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Silver Endeavour</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Feng</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>lday</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>TRIPULANTE</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>LA88</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>2024-09-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>2024-09-22 03:26:00</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O62" s="3" t="inlineStr"/>
+      <c r="P62" s="3" t="inlineStr"/>
+      <c r="Q62" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R62" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S62" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>Fram</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>2024-10-05 00:00:00</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Rommel Noble</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Surban</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Emil Maltha</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Zhou</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>CREW</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
         <is>
           <t>ON</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>LA081</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2023-10-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2023-10-20 16:30:00</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>LA310</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>2024-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>2024-09-23 16:30:00</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>Holiday Inn</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="O63" s="3" t="inlineStr"/>
+      <c r="P63" s="3" t="inlineStr"/>
+      <c r="Q63" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R63" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S63" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>SYLVIA EARLE</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>2025-10-12 00:00:00</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Jaypee</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Costa</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Vivi Kristina</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Bolin</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>TURISTA</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
         <is>
           <t>ON</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>LA081</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2023-10-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2023-10-20 16:30:00</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Silver Endeavour </t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr"/>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Feng</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>lday</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>KL702</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2023-10-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>2023-10-26 10:50:00</t>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>LA310</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>2024-09-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>2024-09-23 15:05:00</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O64" s="3" t="inlineStr"/>
+      <c r="P64" s="3" t="inlineStr"/>
+      <c r="Q64" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R64" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S64" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
